--- a/micron/dist/20261028_美光個股模型_v0.4.2.xlsx
+++ b/micron/dist/20261028_美光個股模型_v0.4.2.xlsx
@@ -61,9 +61,17 @@
     <definedName function="false" hidden="false" name="cqA_14" vbProcedure="false">In!$E$84</definedName>
     <definedName function="false" hidden="false" name="cqA_15" vbProcedure="false">In!$E$85</definedName>
     <definedName function="false" hidden="false" name="cqA_16" vbProcedure="false">In!$E$86</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_hi" vbProcedure="false">In!$F$86</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_lo" vbProcedure="false">In!$D$86</definedName>
     <definedName function="false" hidden="false" name="cqA_17" vbProcedure="false">In!$E$87</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_hi" vbProcedure="false">In!$F$87</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_lo" vbProcedure="false">In!$D$87</definedName>
     <definedName function="false" hidden="false" name="cqA_18" vbProcedure="false">In!$E$88</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_hi" vbProcedure="false">In!$F$88</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_lo" vbProcedure="false">In!$D$88</definedName>
     <definedName function="false" hidden="false" name="cqA_19" vbProcedure="false">In!$E$89</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_hi" vbProcedure="false">In!$F$89</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_lo" vbProcedure="false">In!$D$89</definedName>
     <definedName function="false" hidden="false" name="cqA_8" vbProcedure="false">In!$E$78</definedName>
     <definedName function="false" hidden="false" name="cqA_9" vbProcedure="false">In!$E$79</definedName>
     <definedName function="false" hidden="false" name="cqB_10" vbProcedure="false">In!$E$92</definedName>
@@ -73,9 +81,17 @@
     <definedName function="false" hidden="false" name="cqB_14" vbProcedure="false">In!$E$96</definedName>
     <definedName function="false" hidden="false" name="cqB_15" vbProcedure="false">In!$E$97</definedName>
     <definedName function="false" hidden="false" name="cqB_16" vbProcedure="false">In!$E$98</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_hi" vbProcedure="false">In!$F$98</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_lo" vbProcedure="false">In!$D$98</definedName>
     <definedName function="false" hidden="false" name="cqB_17" vbProcedure="false">In!$E$99</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_hi" vbProcedure="false">In!$F$99</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_lo" vbProcedure="false">In!$D$99</definedName>
     <definedName function="false" hidden="false" name="cqB_18" vbProcedure="false">In!$E$100</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_hi" vbProcedure="false">In!$F$100</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_lo" vbProcedure="false">In!$D$100</definedName>
     <definedName function="false" hidden="false" name="cqB_19" vbProcedure="false">In!$E$101</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_hi" vbProcedure="false">In!$F$101</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_lo" vbProcedure="false">In!$D$101</definedName>
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$90</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$91</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$104</definedName>
@@ -256,9 +272,17 @@
     <definedName function="false" hidden="false" name="nqA_14" vbProcedure="false">In!$E$127</definedName>
     <definedName function="false" hidden="false" name="nqA_15" vbProcedure="false">In!$E$128</definedName>
     <definedName function="false" hidden="false" name="nqA_16" vbProcedure="false">In!$E$129</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_hi" vbProcedure="false">In!$F$129</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_lo" vbProcedure="false">In!$D$129</definedName>
     <definedName function="false" hidden="false" name="nqA_17" vbProcedure="false">In!$E$130</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_hi" vbProcedure="false">In!$F$130</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_lo" vbProcedure="false">In!$D$130</definedName>
     <definedName function="false" hidden="false" name="nqA_18" vbProcedure="false">In!$E$131</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_hi" vbProcedure="false">In!$F$131</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_lo" vbProcedure="false">In!$D$131</definedName>
     <definedName function="false" hidden="false" name="nqA_19" vbProcedure="false">In!$E$132</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_hi" vbProcedure="false">In!$F$132</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_lo" vbProcedure="false">In!$D$132</definedName>
     <definedName function="false" hidden="false" name="nqA_8" vbProcedure="false">In!$E$121</definedName>
     <definedName function="false" hidden="false" name="nqA_9" vbProcedure="false">In!$E$122</definedName>
     <definedName function="false" hidden="false" name="nqB_10" vbProcedure="false">In!$E$135</definedName>
@@ -268,9 +292,17 @@
     <definedName function="false" hidden="false" name="nqB_14" vbProcedure="false">In!$E$139</definedName>
     <definedName function="false" hidden="false" name="nqB_15" vbProcedure="false">In!$E$140</definedName>
     <definedName function="false" hidden="false" name="nqB_16" vbProcedure="false">In!$E$141</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_hi" vbProcedure="false">In!$F$141</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_lo" vbProcedure="false">In!$D$141</definedName>
     <definedName function="false" hidden="false" name="nqB_17" vbProcedure="false">In!$E$142</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_hi" vbProcedure="false">In!$F$142</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_lo" vbProcedure="false">In!$D$142</definedName>
     <definedName function="false" hidden="false" name="nqB_18" vbProcedure="false">In!$E$143</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_hi" vbProcedure="false">In!$F$143</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_lo" vbProcedure="false">In!$D$143</definedName>
     <definedName function="false" hidden="false" name="nqB_19" vbProcedure="false">In!$E$144</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_hi" vbProcedure="false">In!$F$144</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_lo" vbProcedure="false">In!$D$144</definedName>
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$133</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$134</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$147</definedName>
@@ -448,7 +480,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="1067">
   <si>
     <r>
       <rPr>
@@ -5347,33 +5379,74 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美光：產業 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY27 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中 </t>
+    <t xml:space="preserve">Derived</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FQ4-26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法說：產業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">皆中 </t>
     </r>
     <r>
       <rPr>
@@ -5392,7 +5465,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">段；美光供給低於產業</t>
+      <t xml:space="preserve">段；美光供給低於產業（本模型取值）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：原標 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不當</t>
     </r>
   </si>
   <si>
@@ -5675,9 +5786,6 @@
   </si>
   <si>
     <t xml:space="preserve">其他營收（每年）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived</t>
   </si>
   <si>
     <r>
@@ -8190,6 +8298,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -8317,7 +8434,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">緩降</t>
+      <t xml:space="preserve">緩降（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -8889,6 +9025,103 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為本庫外推：標示來源只涵蓋到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核）；區間＝情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同季值</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">cqA_17</t>
   </si>
   <si>
@@ -9177,6 +9410,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -9304,7 +9546,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">溫和回升</t>
+      <t xml:space="preserve">溫和回升（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -11658,6 +11919,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -11690,7 +11960,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力</t>
+      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -12442,6 +12731,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -12504,6 +12802,34 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">NAND $/GB 2028 −68.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -37910,63 +38236,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
         <v>216 ／ 260</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>44</v>
@@ -37997,103 +38323,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>1065</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -38340,18 +38666,18 @@
         <v>0.25</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>48</v>
@@ -38366,7 +38692,7 @@
         <v>0.25</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>63</v>
@@ -38374,10 +38700,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>48</v>
@@ -38392,18 +38718,18 @@
         <v>0.22</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>48</v>
@@ -38418,18 +38744,18 @@
         <v>0.21</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>48</v>
@@ -38444,18 +38770,18 @@
         <v>0.23</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>48</v>
@@ -38475,10 +38801,10 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>53</v>
@@ -38487,7 +38813,7 @@
         <v>0.7</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>84</v>
@@ -38627,7 +38953,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>102</v>
@@ -38653,7 +38979,7 @@
         <v>0.03</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>106</v>
@@ -38673,7 +38999,7 @@
         <v>0.15</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>109</v>
@@ -38765,7 +39091,7 @@
         <v>65</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>121</v>
@@ -39122,7 +39448,7 @@
         <v>68.3</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>160</v>
@@ -39364,7 +39690,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>195</v>
@@ -39384,7 +39710,7 @@
         <v>1.4</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>198</v>
@@ -39404,7 +39730,7 @@
         <v>3</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>201</v>
@@ -39483,7 +39809,7 @@
         <v>-0.025</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H71" s="8" t="s">
         <v>212</v>
@@ -39503,7 +39829,7 @@
         <v>0.125</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>63</v>
@@ -39523,7 +39849,7 @@
         <v>0.475</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>63</v>
@@ -39543,7 +39869,7 @@
         <v>0.95</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>63</v>
@@ -39563,7 +39889,7 @@
         <v>0.605</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>63</v>
@@ -39583,7 +39909,7 @@
         <v>0.155</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>63</v>
@@ -39603,7 +39929,7 @@
         <v>0.125</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>63</v>
@@ -39623,9 +39949,9 @@
         <v>0.03</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H78" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H78" s="4" t="s">
         <v>227</v>
       </c>
     </row>
@@ -39643,7 +39969,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>63</v>
@@ -39663,7 +39989,7 @@
         <v>-0.02</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>63</v>
@@ -39683,7 +40009,7 @@
         <v>-0.03</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>63</v>
@@ -39703,7 +40029,7 @@
         <v>-0.03</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>63</v>
@@ -39723,7 +40049,7 @@
         <v>-0.03</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>63</v>
@@ -39743,7 +40069,7 @@
         <v>-0.02</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>63</v>
@@ -39763,7 +40089,7 @@
         <v>-0.02</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>63</v>
@@ -39779,31 +40105,43 @@
       <c r="C86" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D86" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E86" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F86" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G86" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D87" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E87" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F87" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G87" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>63</v>
@@ -39811,19 +40149,25 @@
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D88" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E88" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F88" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G88" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>63</v>
@@ -39831,19 +40175,25 @@
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D89" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E89" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F89" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G89" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>63</v>
@@ -39851,10 +40201,10 @@
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C90" s="0" t="s">
         <v>48</v>
@@ -39863,18 +40213,18 @@
         <v>0.05</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H90" s="8" t="s">
-        <v>252</v>
+        <v>66</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C91" s="0" t="s">
         <v>48</v>
@@ -39883,7 +40233,7 @@
         <v>0.02</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>63</v>
@@ -39891,10 +40241,10 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>48</v>
@@ -39903,7 +40253,7 @@
         <v>-0.08</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>63</v>
@@ -39911,10 +40261,10 @@
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>48</v>
@@ -39923,7 +40273,7 @@
         <v>-0.15</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>63</v>
@@ -39931,10 +40281,10 @@
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>48</v>
@@ -39943,7 +40293,7 @@
         <v>-0.25</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>63</v>
@@ -39951,10 +40301,10 @@
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>48</v>
@@ -39963,7 +40313,7 @@
         <v>-0.15</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>63</v>
@@ -39971,10 +40321,10 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C96" s="0" t="s">
         <v>48</v>
@@ -39983,7 +40333,7 @@
         <v>-0.1</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>63</v>
@@ -39991,10 +40341,10 @@
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>48</v>
@@ -40003,7 +40353,7 @@
         <v>-0.05</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>63</v>
@@ -40011,39 +40361,51 @@
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D98" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E98" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F98" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G98" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D99" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E99" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F99" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G99" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>63</v>
@@ -40051,19 +40413,25 @@
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D100" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E100" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F100" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G100" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>63</v>
@@ -40071,19 +40439,25 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D101" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E101" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F101" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G101" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>63</v>
@@ -40091,10 +40465,10 @@
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C102" s="0" t="s">
         <v>48</v>
@@ -40112,15 +40486,15 @@
         <v>49</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>48</v>
@@ -40143,10 +40517,10 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>48</v>
@@ -40169,10 +40543,10 @@
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>48</v>
@@ -40195,10 +40569,10 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>48</v>
@@ -40221,10 +40595,10 @@
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>48</v>
@@ -40247,10 +40621,10 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>48</v>
@@ -40273,10 +40647,10 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>48</v>
@@ -40299,10 +40673,10 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>48</v>
@@ -40325,10 +40699,10 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>48</v>
@@ -40351,10 +40725,10 @@
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>48</v>
@@ -40377,10 +40751,10 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>48</v>
@@ -40403,10 +40777,10 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>48</v>
@@ -40415,18 +40789,18 @@
         <v>0</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>48</v>
@@ -40435,7 +40809,7 @@
         <v>0.05</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>63</v>
@@ -40443,10 +40817,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>48</v>
@@ -40455,7 +40829,7 @@
         <v>0.3</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>63</v>
@@ -40463,10 +40837,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>48</v>
@@ -40475,7 +40849,7 @@
         <v>0.875</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>63</v>
@@ -40483,10 +40857,10 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>48</v>
@@ -40495,7 +40869,7 @@
         <v>0.725</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>63</v>
@@ -40503,10 +40877,10 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>48</v>
@@ -40515,7 +40889,7 @@
         <v>0.15</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>63</v>
@@ -40523,10 +40897,10 @@
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>48</v>
@@ -40535,7 +40909,7 @@
         <v>0.175</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H120" s="4" t="s">
         <v>63</v>
@@ -40543,10 +40917,10 @@
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>48</v>
@@ -40555,18 +40929,18 @@
         <v>0.03</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H121" s="8" t="s">
-        <v>317</v>
+        <v>66</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>48</v>
@@ -40575,7 +40949,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>63</v>
@@ -40583,10 +40957,10 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>48</v>
@@ -40595,7 +40969,7 @@
         <v>-0.05</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>63</v>
@@ -40603,10 +40977,10 @@
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>48</v>
@@ -40615,7 +40989,7 @@
         <v>-0.07</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>63</v>
@@ -40623,10 +40997,10 @@
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>48</v>
@@ -40635,7 +41009,7 @@
         <v>-0.05</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>63</v>
@@ -40643,10 +41017,10 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>48</v>
@@ -40655,7 +41029,7 @@
         <v>-0.05</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>63</v>
@@ -40663,10 +41037,10 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>48</v>
@@ -40675,7 +41049,7 @@
         <v>-0.05</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>63</v>
@@ -40683,10 +41057,10 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>48</v>
@@ -40695,7 +41069,7 @@
         <v>-0.05</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>63</v>
@@ -40703,39 +41077,51 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D129" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E129" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F129" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G129" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D130" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E130" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F130" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G130" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>63</v>
@@ -40743,19 +41129,25 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D131" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E131" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F131" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G131" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>63</v>
@@ -40763,19 +41155,25 @@
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D132" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E132" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F132" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G132" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H132" s="4" t="s">
         <v>63</v>
@@ -40783,10 +41181,10 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>48</v>
@@ -40795,18 +41193,18 @@
         <v>0.05</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H133" s="8" t="s">
-        <v>342</v>
+        <v>66</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C134" s="0" t="s">
         <v>48</v>
@@ -40815,7 +41213,7 @@
         <v>0.02</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>63</v>
@@ -40823,10 +41221,10 @@
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>48</v>
@@ -40835,7 +41233,7 @@
         <v>-0.1</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>63</v>
@@ -40843,10 +41241,10 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>48</v>
@@ -40855,7 +41253,7 @@
         <v>-0.2</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>63</v>
@@ -40863,10 +41261,10 @@
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C137" s="0" t="s">
         <v>48</v>
@@ -40875,7 +41273,7 @@
         <v>-0.3</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>63</v>
@@ -40883,10 +41281,10 @@
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C138" s="0" t="s">
         <v>48</v>
@@ -40895,7 +41293,7 @@
         <v>-0.25</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>63</v>
@@ -40903,10 +41301,10 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>48</v>
@@ -40915,7 +41313,7 @@
         <v>-0.2</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>63</v>
@@ -40923,10 +41321,10 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>48</v>
@@ -40935,7 +41333,7 @@
         <v>-0.1</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>63</v>
@@ -40943,39 +41341,51 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D141" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E141" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F141" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G141" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="H141" s="8" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D142" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E142" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F142" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G142" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>63</v>
@@ -40983,19 +41393,25 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C143" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D143" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E143" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F143" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G143" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>63</v>
@@ -41003,19 +41419,25 @@
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C144" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D144" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E144" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F144" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G144" s="8" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="H144" s="4" t="s">
         <v>63</v>
@@ -41023,10 +41445,10 @@
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>48</v>
@@ -41044,15 +41466,15 @@
         <v>49</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>48</v>
@@ -41075,10 +41497,10 @@
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>48</v>
@@ -41101,10 +41523,10 @@
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>48</v>
@@ -41127,10 +41549,10 @@
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C149" s="0" t="s">
         <v>48</v>
@@ -41153,10 +41575,10 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>48</v>
@@ -41179,10 +41601,10 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C151" s="0" t="s">
         <v>48</v>
@@ -41205,10 +41627,10 @@
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C152" s="0" t="s">
         <v>48</v>
@@ -41231,10 +41653,10 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C153" s="0" t="s">
         <v>48</v>
@@ -41257,10 +41679,10 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>48</v>
@@ -41283,10 +41705,10 @@
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>48</v>
@@ -41309,10 +41731,10 @@
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C156" s="0" t="s">
         <v>48</v>
@@ -41335,44 +41757,44 @@
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E158" s="7" t="n">
         <v>5.4</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E159" s="7" t="n">
         <v>2.4</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>63</v>
@@ -41380,19 +41802,19 @@
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E160" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>63</v>
@@ -41400,19 +41822,19 @@
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E161" s="7" t="n">
         <v>260</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>63</v>
@@ -41420,19 +41842,19 @@
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="C162" s="0" t="s">
         <v>402</v>
-      </c>
-      <c r="B162" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="C162" s="0" t="s">
-        <v>401</v>
       </c>
       <c r="E162" s="7" t="n">
         <v>280</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>63</v>
@@ -41440,19 +41862,19 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E163" s="7" t="n">
         <v>288</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>63</v>
@@ -41460,39 +41882,39 @@
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E164" s="7" t="n">
         <v>1.7</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E165" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>63</v>
@@ -41500,19 +41922,19 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E166" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>63</v>
@@ -41520,19 +41942,19 @@
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E167" s="7" t="n">
         <v>288</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>63</v>
@@ -41540,19 +41962,19 @@
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E168" s="7" t="n">
         <v>288</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>63</v>
@@ -41560,19 +41982,19 @@
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>288</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>63</v>
@@ -41580,13 +42002,13 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D170" s="7" t="n">
         <v>0</v>
@@ -41601,18 +42023,18 @@
         <v>49</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D171" s="7" t="n">
         <v>0</v>
@@ -41632,13 +42054,13 @@
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D172" s="7" t="n">
         <v>1</v>
@@ -41658,39 +42080,39 @@
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E173" s="7" t="n">
         <v>1024</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E174" s="7" t="n">
         <v>1024</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>63</v>
@@ -41698,19 +42120,19 @@
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E175" s="7" t="n">
         <v>1024</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>63</v>
@@ -41718,39 +42140,39 @@
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E176" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E177" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>63</v>
@@ -41758,19 +42180,19 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E178" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>63</v>
@@ -41778,19 +42200,19 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E179" s="7" t="n">
         <v>141</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>63</v>
@@ -41798,19 +42220,19 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E180" s="7" t="n">
         <v>141</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>63</v>
@@ -41818,19 +42240,19 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E181" s="7" t="n">
         <v>141</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>63</v>
@@ -41838,13 +42260,13 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D182" s="7" t="n">
         <v>0.6</v>
@@ -41856,21 +42278,21 @@
         <v>0.9</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D183" s="7" t="n">
         <v>1.2</v>
@@ -41882,7 +42304,7 @@
         <v>1.8</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>63</v>
@@ -41890,13 +42312,13 @@
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D184" s="7" t="n">
         <v>1.5</v>
@@ -41908,7 +42330,7 @@
         <v>2.5</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>63</v>
@@ -41916,13 +42338,13 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D185" s="7" t="n">
         <v>288</v>
@@ -41934,7 +42356,7 @@
         <v>288</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>63</v>
@@ -41942,13 +42364,13 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D186" s="7" t="n">
         <v>288</v>
@@ -41960,7 +42382,7 @@
         <v>432</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>63</v>
@@ -41968,13 +42390,13 @@
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D187" s="7" t="n">
         <v>432</v>
@@ -41986,7 +42408,7 @@
         <v>432</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>63</v>
@@ -41994,39 +42416,39 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E188" s="7" t="n">
         <v>3.85</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E189" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>63</v>
@@ -42034,19 +42456,19 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E190" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>63</v>
@@ -42054,19 +42476,19 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E191" s="7" t="n">
         <v>192</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>63</v>
@@ -42074,19 +42496,19 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E192" s="7" t="n">
         <v>250</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H192" s="4" t="s">
         <v>63</v>
@@ -42094,19 +42516,19 @@
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E193" s="7" t="n">
         <v>288</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>63</v>
@@ -42114,13 +42536,13 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D194" s="7" t="n">
         <v>1.5</v>
@@ -42135,18 +42557,18 @@
         <v>49</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D195" s="7" t="n">
         <v>2</v>
@@ -42166,13 +42588,13 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D196" s="7" t="n">
         <v>2</v>
@@ -42192,13 +42614,13 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D197" s="7" t="n">
         <v>96</v>
@@ -42218,13 +42640,13 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D198" s="7" t="n">
         <v>120</v>
@@ -42244,13 +42666,13 @@
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D199" s="7" t="n">
         <v>144</v>
@@ -42270,13 +42692,13 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D200" s="7" t="n">
         <v>0.5</v>
@@ -42288,21 +42710,21 @@
         <v>1.5</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D201" s="7" t="n">
         <v>3</v>
@@ -42314,7 +42736,7 @@
         <v>6</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>63</v>
@@ -42322,13 +42744,13 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D202" s="7" t="n">
         <v>3.5</v>
@@ -42340,7 +42762,7 @@
         <v>7</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H202" s="4" t="s">
         <v>63</v>
@@ -42348,13 +42770,13 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D203" s="7" t="n">
         <v>100</v>
@@ -42366,7 +42788,7 @@
         <v>200</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>63</v>
@@ -42374,13 +42796,13 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D204" s="7" t="n">
         <v>150</v>
@@ -42392,7 +42814,7 @@
         <v>250</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>63</v>
@@ -42400,13 +42822,13 @@
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D205" s="7" t="n">
         <v>200</v>
@@ -42418,7 +42840,7 @@
         <v>300</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>63</v>
@@ -42426,15 +42848,15 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>194</v>
@@ -42443,18 +42865,18 @@
         <v>1</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>194</v>
@@ -42463,7 +42885,7 @@
         <v>1</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>63</v>
@@ -42471,10 +42893,10 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>194</v>
@@ -42497,10 +42919,10 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C210" s="0" t="s">
         <v>194</v>
@@ -42523,10 +42945,10 @@
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C211" s="0" t="s">
         <v>194</v>
@@ -42549,10 +42971,10 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C212" s="0" t="s">
         <v>194</v>
@@ -42575,18 +42997,18 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D214" s="7" t="n">
         <v>34</v>
@@ -42601,15 +43023,15 @@
         <v>40</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>48</v>
@@ -42624,18 +43046,18 @@
         <v>0.8</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C216" s="0" t="s">
         <v>194</v>
@@ -42653,15 +43075,15 @@
         <v>49</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>48</v>
@@ -42676,18 +43098,18 @@
         <v>0.63</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>48</v>
@@ -42705,18 +43127,18 @@
         <v>49</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D219" s="7" t="n">
         <v>12.5</v>
@@ -42728,18 +43150,18 @@
         <v>16</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>48</v>
@@ -42754,18 +43176,18 @@
         <v>1.21</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>48</v>
@@ -42780,18 +43202,18 @@
         <v>0.25</v>
       </c>
       <c r="G221" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>48</v>
@@ -42809,15 +43231,15 @@
         <v>49</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C223" s="0" t="s">
         <v>48</v>
@@ -42835,15 +43257,15 @@
         <v>49</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>48</v>
@@ -42861,15 +43283,15 @@
         <v>49</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>48</v>
@@ -42887,15 +43309,15 @@
         <v>49</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>48</v>
@@ -42913,15 +43335,15 @@
         <v>49</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>48</v>
@@ -42939,15 +43361,15 @@
         <v>49</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>48</v>
@@ -42965,23 +43387,23 @@
         <v>49</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D230" s="7" t="n">
         <v>340</v>
@@ -42996,18 +43418,18 @@
         <v>186</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D231" s="7" t="n">
         <v>38</v>
@@ -43019,21 +43441,21 @@
         <v>48</v>
       </c>
       <c r="G231" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D232" s="7" t="n">
         <v>3.5</v>
@@ -43045,83 +43467,83 @@
         <v>4.9</v>
       </c>
       <c r="G232" s="8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E233" s="7" t="n">
         <v>54.6</v>
       </c>
       <c r="G233" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E234" s="7" t="n">
         <v>77.4</v>
       </c>
       <c r="G234" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E235" s="7" t="n">
         <v>152.8</v>
       </c>
       <c r="G235" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>48</v>
@@ -43135,15 +43557,15 @@
         <v>49</v>
       </c>
       <c r="H237" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>48</v>
@@ -43157,15 +43579,15 @@
         <v>49</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>48</v>
@@ -43179,15 +43601,15 @@
         <v>49</v>
       </c>
       <c r="H239" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>48</v>
@@ -43201,15 +43623,15 @@
         <v>49</v>
       </c>
       <c r="H240" s="9" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>48</v>
@@ -43223,15 +43645,15 @@
         <v>49</v>
       </c>
       <c r="H241" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>48</v>
@@ -43243,18 +43665,18 @@
       </c>
       <c r="F242" s="9"/>
       <c r="G242" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H242" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>48</v>
@@ -43268,15 +43690,15 @@
         <v>49</v>
       </c>
       <c r="H243" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>48</v>
@@ -43288,18 +43710,18 @@
       </c>
       <c r="F244" s="9"/>
       <c r="G244" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H244" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C245" s="9" t="s">
         <v>48</v>
@@ -43314,15 +43736,15 @@
         <v>49</v>
       </c>
       <c r="H245" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C246" s="9" t="s">
         <v>48</v>
@@ -43337,15 +43759,15 @@
         <v>49</v>
       </c>
       <c r="H246" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>48</v>
@@ -43360,15 +43782,15 @@
         <v>49</v>
       </c>
       <c r="H247" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>194</v>
@@ -43382,15 +43804,15 @@
         <v>49</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>194</v>
@@ -43404,15 +43826,15 @@
         <v>49</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>48</v>
@@ -43424,18 +43846,18 @@
       </c>
       <c r="F250" s="9"/>
       <c r="G250" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>48</v>
@@ -43447,18 +43869,18 @@
       </c>
       <c r="F251" s="9"/>
       <c r="G251" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>48</v>
@@ -43470,18 +43892,18 @@
       </c>
       <c r="F252" s="9"/>
       <c r="G252" s="9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>39</v>
@@ -43496,18 +43918,18 @@
         <v>3000</v>
       </c>
       <c r="G253" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>39</v>
@@ -43518,18 +43940,18 @@
       </c>
       <c r="F254" s="9"/>
       <c r="G254" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>39</v>
@@ -43540,18 +43962,18 @@
       </c>
       <c r="F255" s="9"/>
       <c r="G255" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>39</v>
@@ -43562,10 +43984,10 @@
       </c>
       <c r="F256" s="9"/>
       <c r="G256" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H256" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -43593,83 +44015,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -43753,10 +44175,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -43840,10 +44262,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -43927,10 +44349,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -44014,10 +44436,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -44101,10 +44523,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>662</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>661</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -44188,50 +44610,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -44272,10 +44694,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -44316,10 +44738,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -44360,10 +44782,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -44404,10 +44826,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -44448,10 +44870,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>662</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>661</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -44516,7 +44938,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44527,35 +44949,35 @@
         <v>30</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -44572,10 +44994,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>678</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>677</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -44592,10 +45014,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -44612,10 +45034,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -44632,10 +45054,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -44652,10 +45074,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -44672,10 +45094,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -44692,10 +45114,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -44712,10 +45134,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -44736,10 +45158,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>687</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>686</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -44760,10 +45182,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">u_bw_26+u_rb_26+u_ru_26+u_hp_26+u_amd_26+u_tpu_26+u_trn_26+u_oth_26</f>
@@ -44778,15 +45200,15 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">D13*1000/D15</f>
@@ -44803,10 +45225,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -44829,12 +45251,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>194</v>
@@ -44854,12 +45276,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>194</v>
@@ -44879,12 +45301,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>194</v>
@@ -44904,15 +45326,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -44933,10 +45355,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -44957,10 +45379,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -44981,10 +45403,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -45007,15 +45429,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -45040,10 +45462,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -45068,10 +45490,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -45092,10 +45514,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -45116,10 +45538,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -45140,10 +45562,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45168,10 +45590,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45196,10 +45618,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -45224,10 +45646,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -45252,10 +45674,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -45280,10 +45702,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -45308,15 +45730,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -45325,22 +45747,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>48</v>
@@ -45352,10 +45774,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">nv_dc26/nv_content</f>
@@ -45366,15 +45788,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -45391,7 +45813,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>48</v>
@@ -45430,7 +45852,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45438,36 +45860,36 @@
         <v>29</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>8.709</v>
@@ -45500,7 +45922,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>6.4</v>
@@ -45533,7 +45955,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>2.241</v>
@@ -45566,7 +45988,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">B4-B5-B6</f>
@@ -45607,7 +46029,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B4*(1-0.384)</f>
@@ -45648,7 +46070,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">B4-B8-B10</f>
@@ -45689,7 +46111,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>2.174</v>
@@ -45722,7 +46144,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -45763,7 +46185,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>1.87</v>
@@ -45796,7 +46218,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>2.03</v>
@@ -45829,7 +46251,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>1</v>
@@ -45837,7 +46259,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>1</v>
@@ -45845,17 +46267,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>2.648</v>
@@ -45888,7 +46310,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>2.292</v>
@@ -45921,7 +46343,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>2.608</v>
@@ -45954,7 +46376,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>1.158</v>
@@ -45987,7 +46409,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B25" s="21" t="n">
         <f aca="false">B21+B22+B23+B24-B4</f>
@@ -46028,12 +46450,12 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -46062,12 +46484,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46075,72 +46497,72 @@
         <v>29</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -46189,7 +46611,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -46232,12 +46654,12 @@
         <v>54.0906594963139</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!C33/4*sh25+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*1</f>
@@ -46280,12 +46702,12 @@
         <v>24.77309368356</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -46330,7 +46752,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -46375,7 +46797,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -46420,7 +46842,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -46469,7 +46891,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -46510,7 +46932,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -46553,12 +46975,12 @@
         <v>47.6521514233851</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -46603,7 +47025,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -46652,7 +47074,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -46701,7 +47123,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -46746,7 +47168,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -46791,7 +47213,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -46870,12 +47292,12 @@
         <v>67.3959611855303</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -46920,7 +47342,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -47003,12 +47425,12 @@
         <v>7.90574229843858</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -47053,7 +47475,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -47098,7 +47520,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -47143,7 +47565,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -47186,12 +47608,12 @@
         <v>6.21314932975986</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(0)+extra_eq-C24-C23</f>
@@ -47236,7 +47658,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(0)+(0)-capex_rem+extra_eq-C24-C23</f>
@@ -47281,7 +47703,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -47362,7 +47784,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C28" s="23" t="n">
         <f aca="false">C25/C27*1000</f>
@@ -47407,7 +47829,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">C20/C27*1000</f>
@@ -47488,7 +47910,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -47533,7 +47955,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!C24/4*sh25+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -47578,7 +48000,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -47655,7 +48077,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -47764,30 +48186,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47799,10 +48221,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E4" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -47819,17 +48241,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E5" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -47846,17 +48268,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E6" s="23" t="n">
         <f aca="false">Y!C28</f>
@@ -47880,10 +48302,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E7" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -47900,17 +48322,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -47927,17 +48349,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E9" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -47961,10 +48383,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -47981,17 +48403,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E11" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -48008,17 +48430,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">Y!G28</f>
@@ -48042,10 +48464,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48062,17 +48484,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E14" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48089,17 +48511,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E15" s="23" t="n">
         <f aca="false">Y!J28</f>
@@ -48123,10 +48545,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E16" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48143,17 +48565,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E17" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48170,17 +48592,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E18" s="23" t="n">
         <f aca="false">Y!E28</f>
@@ -48204,10 +48626,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E19" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48224,17 +48646,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48251,17 +48673,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E21" s="23" t="n">
         <f aca="false">Y!H28</f>
@@ -48285,10 +48707,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -48305,17 +48727,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -48332,17 +48754,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -48366,10 +48788,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E25" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -48386,17 +48808,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E26" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -48413,17 +48835,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">Y!F28</f>
@@ -48447,10 +48869,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E28" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -48467,17 +48889,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -48494,17 +48916,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E30" s="23" t="n">
         <f aca="false">Y!I28</f>
@@ -48528,10 +48950,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E31" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -48548,17 +48970,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E32" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -48575,17 +48997,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E33" s="23" t="n">
         <f aca="false">Y!L28</f>
@@ -48609,10 +49031,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E34" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -48636,10 +49058,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E35" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -48663,10 +49085,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E36" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -48690,10 +49112,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E37" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -48717,10 +49139,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E38" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -48744,10 +49166,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E39" s="23" t="n">
         <f aca="false">Y!G29</f>
@@ -48771,10 +49193,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -48798,10 +49220,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -48825,10 +49247,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">Y!J29</f>
@@ -48852,10 +49274,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -48879,10 +49301,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -48906,10 +49328,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -48933,10 +49355,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -48960,10 +49382,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -48987,10 +49409,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E48" s="23" t="n">
         <f aca="false">Y!H29</f>
@@ -49014,10 +49436,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49041,10 +49463,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E50" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49068,10 +49490,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E51" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -49095,10 +49517,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E52" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49122,10 +49544,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49149,10 +49571,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E54" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -49176,10 +49598,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E55" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49203,10 +49625,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E56" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49230,10 +49652,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E57" s="23" t="n">
         <f aca="false">Y!I29</f>
@@ -49257,10 +49679,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E58" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49284,10 +49706,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E59" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49311,10 +49733,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E60" s="23" t="n">
         <f aca="false">Y!L29</f>
@@ -49331,29 +49753,29 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>1.29</v>
@@ -49370,7 +49792,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>1.78</v>
@@ -49387,7 +49809,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>1.79</v>
@@ -49404,7 +49826,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>1.33</v>
@@ -49421,7 +49843,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>1.27</v>
@@ -49438,7 +49860,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>1.83</v>
@@ -49455,7 +49877,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>1.22</v>
@@ -49472,7 +49894,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>1.72</v>
@@ -49489,7 +49911,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>2.35</v>
@@ -49506,7 +49928,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>2.46</v>
@@ -49523,41 +49945,41 @@
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B82" s="18" t="n">
         <v>1.29</v>
@@ -49566,12 +49988,12 @@
         <v>1.83</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B83" s="18" t="n">
         <v>1.78</v>
@@ -49582,7 +50004,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B84" s="18" t="n">
         <v>1.79</v>
@@ -49593,7 +50015,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B85" s="18" t="n">
         <v>1.33</v>
@@ -49604,7 +50026,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B86" s="18" t="n">
         <v>1.27</v>
@@ -49615,7 +50037,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B87" s="18" t="n">
         <v>1.83</v>
@@ -49626,7 +50048,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B88" s="18" t="n">
         <v>1.22</v>
@@ -49637,7 +50059,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B89" s="18" t="n">
         <v>1.72</v>
@@ -49648,7 +50070,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B90" s="18" t="n">
         <v>2.35</v>
@@ -49659,7 +50081,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B91" s="18" t="n">
         <v>2.46</v>
@@ -49670,7 +50092,7 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B92" s="14" t="n">
         <f aca="false">PERCENTILE(B82:B91,0.25)</f>
@@ -49683,7 +50105,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B93" s="14" t="n">
         <f aca="false">MEDIAN(B82:B91)</f>
@@ -49696,7 +50118,7 @@
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B94" s="14" t="n">
         <f aca="false">PERCENTILE(B82:B91,0.75)</f>
@@ -49709,7 +50131,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B95" s="14" t="n">
         <f aca="false">MIN(B82:B91)</f>
@@ -49722,7 +50144,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B96" s="14" t="n">
         <f aca="false">MAX(B82:B91)</f>
@@ -49735,7 +50157,7 @@
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B92),2)</f>
@@ -49744,7 +50166,7 @@
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B98" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B93),2)</f>
@@ -49753,7 +50175,7 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B94),2)</f>
@@ -49762,7 +50184,7 @@
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B100" s="14" t="n">
         <f aca="false">ROUND(MIN(B95),2)</f>
@@ -49771,7 +50193,7 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B101" s="14" t="n">
         <f aca="false">ROUND(MAX(B96),2)</f>
@@ -49780,7 +50202,7 @@
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B102" s="14" t="n">
         <f aca="false">ROUND(C92,2)</f>
@@ -49789,7 +50211,7 @@
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B103" s="14" t="n">
         <f aca="false">ROUND(C93,2)</f>
@@ -49798,7 +50220,7 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B104" s="14" t="n">
         <f aca="false">ROUND(C94,2)</f>
@@ -49807,48 +50229,48 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C108" s="14" t="n">
         <f aca="false">B97</f>
         <v>1.3</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E108" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -49869,17 +50291,17 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C109" s="14" t="n">
         <f aca="false">B98</f>
         <v>1.75</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E109" s="23" t="n">
         <f aca="false">Y!D28</f>
@@ -49900,17 +50322,17 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C110" s="14" t="n">
         <f aca="false">B99</f>
         <v>1.82</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E110" s="23" t="n">
         <f aca="false">Y!K28</f>
@@ -49931,47 +50353,47 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B115" s="14" t="str">
         <f aca="false">IF(E65&gt;0,B65*C65/E65,"")</f>
         <v/>
       </c>
       <c r="C115" s="8" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">IF(E66&gt;0,B66*C66/E66,"")</f>
         <v>6.51314207113382</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">IF(E67&gt;0,B67*C67/E67,"")</f>
@@ -49980,7 +50402,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B118" s="14" t="n">
         <f aca="false">IF(E68&gt;0,B68*C68/E68,"")</f>
@@ -49989,7 +50411,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B119" s="14" t="n">
         <f aca="false">IF(E69&gt;0,B69*C69/E69,"")</f>
@@ -49998,7 +50420,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B120" s="14" t="n">
         <f aca="false">IF(E70&gt;0,B70*C70/E70,"")</f>
@@ -50007,7 +50429,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B121" s="14" t="n">
         <f aca="false">IF(E71&gt;0,B71*C71/E71,"")</f>
@@ -50016,7 +50438,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B122" s="14" t="str">
         <f aca="false">IF(E72&gt;0,B72*C72/E72,"")</f>
@@ -50025,7 +50447,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B123" s="14" t="n">
         <f aca="false">IF(E73&gt;0,B73*C73/E73,"")</f>
@@ -50034,7 +50456,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B124" s="14" t="n">
         <f aca="false">IF(E74&gt;0,B74*C74/E74,"")</f>
@@ -50043,7 +50465,7 @@
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B125" s="14" t="n">
         <f aca="false">PERCENTILE(B115:B124,0.25)</f>
@@ -50052,7 +50474,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B126" s="14" t="n">
         <f aca="false">MEDIAN(B115:B124)</f>
@@ -50061,7 +50483,7 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B127" s="14" t="n">
         <f aca="false">PERCENTILE(B115:B124,0.75)</f>
@@ -50070,7 +50492,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B128" s="14" t="n">
         <f aca="false">MIN(B115:B124)</f>
@@ -50079,7 +50501,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B129" s="14" t="n">
         <f aca="false">MAX(B115:B124)</f>
@@ -50088,7 +50510,7 @@
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B130" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B125),2)</f>
@@ -50097,7 +50519,7 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B131" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B126),2)</f>
@@ -50106,7 +50528,7 @@
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B132" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B127),2)</f>
@@ -50115,7 +50537,7 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B133" s="14" t="n">
         <f aca="false">ROUND(MIN(B128),2)</f>
@@ -50124,7 +50546,7 @@
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B134" s="14" t="n">
         <f aca="false">ROUND(MAX(B129),2)</f>
@@ -50133,48 +50555,48 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C138" s="14" t="n">
         <f aca="false">B130</f>
         <v>6.88</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E138" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50195,17 +50617,17 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C139" s="14" t="n">
         <f aca="false">B131</f>
         <v>10.64</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E139" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50226,17 +50648,17 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C140" s="14" t="n">
         <f aca="false">B132</f>
         <v>16.31</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E140" s="23" t="n">
         <f aca="false">Y!K29</f>
@@ -50257,35 +50679,35 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B145" s="14" t="n">
         <f aca="false">B65*C65/(C65+D65)</f>
         <v>1.18874055992067</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B146" s="14" t="n">
         <f aca="false">B66*C66/(C66+D66)</f>
@@ -50294,7 +50716,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B147" s="14" t="n">
         <f aca="false">B67*C67/(C67+D67)</f>
@@ -50303,7 +50725,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B148" s="14" t="n">
         <f aca="false">B68*C68/(C68+D68)</f>
@@ -50312,7 +50734,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B149" s="14" t="n">
         <f aca="false">B69*C69/(C69+D69)</f>
@@ -50321,7 +50743,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B150" s="14" t="n">
         <f aca="false">B70*C70/(C70+D70)</f>
@@ -50330,7 +50752,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B151" s="14" t="n">
         <f aca="false">B71*C71/(C71+D71)</f>
@@ -50339,7 +50761,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B152" s="14" t="n">
         <f aca="false">B72*C72/(C72+D72)</f>
@@ -50348,7 +50770,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B153" s="14" t="n">
         <f aca="false">B73*C73/(C73+D73)</f>
@@ -50357,7 +50779,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">B74*C74/(C74+D74)</f>
@@ -50366,7 +50788,7 @@
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B155" s="14" t="n">
         <f aca="false">PERCENTILE(B145:B154,0.25)</f>
@@ -50375,7 +50797,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B156" s="14" t="n">
         <f aca="false">MEDIAN(B145:B154)</f>
@@ -50384,7 +50806,7 @@
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B157" s="14" t="n">
         <f aca="false">PERCENTILE(B145:B154,0.75)</f>
@@ -50393,7 +50815,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B158" s="14" t="n">
         <f aca="false">MIN(B145:B154)</f>
@@ -50402,7 +50824,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B159" s="14" t="n">
         <f aca="false">MAX(B145:B154)</f>
@@ -50411,7 +50833,7 @@
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B160" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B155),2)</f>
@@ -50420,7 +50842,7 @@
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B161" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B156),2)</f>
@@ -50429,7 +50851,7 @@
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B162" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B157),2)</f>
@@ -50438,7 +50860,7 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B163" s="14" t="n">
         <f aca="false">ROUND(MIN(B158),2)</f>
@@ -50447,7 +50869,7 @@
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B164" s="14" t="n">
         <f aca="false">ROUND(MAX(B159),2)</f>
@@ -50456,48 +50878,48 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C168" s="14" t="n">
         <f aca="false">B160</f>
         <v>1.2</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E168" s="23" t="n">
         <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
@@ -50518,17 +50940,17 @@
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C169" s="14" t="n">
         <f aca="false">B161</f>
         <v>1.56</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E169" s="23" t="n">
         <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
@@ -50549,17 +50971,17 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C170" s="14" t="n">
         <f aca="false">B162</f>
         <v>1.77</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E170" s="23" t="n">
         <f aca="false">(Y!K25+$D$74+Y!J24+Y!K24)/Y!K27*1000</f>
@@ -50580,12 +51002,12 @@
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50593,29 +51015,29 @@
         <v>29</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B177" s="23" t="n">
         <f aca="false">Y!D29</f>
@@ -50632,7 +51054,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B178" s="23" t="n">
         <f aca="false">Y!E29</f>
@@ -50649,7 +51071,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B179" s="23" t="n">
         <f aca="false">Y!F29</f>
@@ -50666,7 +51088,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B180" s="23" t="n">
         <f aca="false">Y!M29</f>
@@ -50683,7 +51105,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B181" s="23" t="n">
         <f aca="false">Y!N29</f>
@@ -50700,7 +51122,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B182" s="23" t="n">
         <f aca="false">Y!O29</f>
@@ -50717,27 +51139,27 @@
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B184" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.111940298507463</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B185" s="23" t="n">
         <f aca="false">Y!D22/Y!D27*1000</f>
@@ -50754,7 +51176,7 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B186" s="23" t="n">
         <f aca="false">Y!E22/Y!E27*1000</f>
@@ -50771,7 +51193,7 @@
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B187" s="23" t="n">
         <f aca="false">Y!F22/Y!F27*1000</f>
@@ -50788,7 +51210,7 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B188" s="23" t="n">
         <f aca="false">B180*(1-$B$184)</f>
@@ -50805,7 +51227,7 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B189" s="23" t="n">
         <f aca="false">B181*(1-$B$184)</f>
@@ -50822,7 +51244,7 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B190" s="23" t="n">
         <f aca="false">B182*(1-$B$184)</f>
@@ -50839,7 +51261,7 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B191" s="23" t="n">
         <f aca="false">SUMPRODUCT(B185:B190,1/(1+tp_r)^{1;2;3;4;5;6})+B190*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -50854,12 +51276,12 @@
         <v>292.633169398705</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B192" s="23" t="n">
         <f aca="false">B191*(1+tp_r)</f>
@@ -50876,36 +51298,36 @@
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B193" s="27" t="n">
         <f aca="false">tp_wA*B192+tp_wB*C192+tp_wC*D192</f>
         <v>932.626083378287</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>34</v>
@@ -50913,135 +51335,135 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C197" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C198" s="18" t="n">
         <v>1.26</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C199" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C200" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B201" s="14" t="n">
         <f aca="false">MEDIAN(C197:C200)</f>
         <v>1.505</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B202" s="23" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>289.403890275058</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B203" s="27" t="n">
         <f aca="false">B201*B202</f>
         <v>435.552854863962</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B204" s="23" t="n">
         <f aca="false">tp_wA*(0*Y!D29+1*Y!E29)+tp_wB*(0*Y!G29+1*Y!H29)+tp_wC*(0*Y!J29+1*Y!K29)</f>
         <v>157.327188920468</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51049,29 +51471,29 @@
         <v>29</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B208" s="27" t="n">
         <f aca="false">tp_w_dcf*B193+(1-tp_w_dcf)*B203</f>
         <v>684.089469121124</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B209" s="23" t="n">
         <f aca="false">B203</f>
@@ -51080,31 +51502,31 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B210" s="23" t="n">
         <f aca="false">cons_tp</f>
         <v>1560.57</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B211" s="19" t="n">
         <f aca="false">B208/px-1</f>
         <v>-0.220455279902998</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B212" s="19" t="n">
         <f aca="false">B209/px-1</f>
@@ -51113,7 +51535,7 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B213" s="28" t="n">
         <f aca="false">B192/px</f>
@@ -51128,36 +51550,36 @@
         <v>0.366812701656402</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B214" s="19" t="n">
         <f aca="false">B202/cons_bvps28-1</f>
         <v>-0.308308101637052</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B215" s="19" t="n">
         <f aca="false">B204/(0*cons_eps27+1*cons_eps28)-1</f>
         <v>-0.21766688751632</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B216" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B201-1</f>
@@ -51170,19 +51592,19 @@
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B217" s="29" t="str">
         <f aca="false">TEXT(D192,"#,##0")&amp;"～"&amp;TEXT(B192,"#,##0")</f>
         <v>322～1,714</v>
       </c>
       <c r="E217" s="8" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B218" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$82:$B$91),1,IF(px/Y!E28&lt;=MIN($B$82:$B$91),0,PERCENTRANK($B$82:$B$91,px/Y!E28)))</f>
@@ -51197,12 +51619,12 @@
         <v>1</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B219" s="0" t="str">
         <f aca="false">"DCF：股東現金流 FY2027–FY2029 用每股（淨利＋折舊－資本支出），FY2030–FY2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 FY2024–FY2026 平均約 36%；明確期＋永續，基準日 2026 年底。Comparable：SK 海力士、三星、鎧俠、南亞科前瞻 P/B 中位數 × FY2028 年底每股淨值（情境加權）。收斂期（FY"&amp;"2030–FY2032）淨利率收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 FY2032 中段水準為基礎。偏誤：FY2027–FY2029 仍為高峰期盈餘，DCF 仍可能偏高估；美光大量買回使帳面淨值偏低，同業 P/B 套用在美光淨值上，Comparable 偏低估。情境對應：A＝順利、B＝平平、C＝不如預期（原"&amp;"為 TrendForce／BofA 型價格情境）。"&amp;IF(MAX(B213:D213)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -51211,7 +51633,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51219,29 +51641,29 @@
         <v>29</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B223" s="23" t="n">
         <f aca="false">tp_wA*B225+tp_wB*B226+tp_wC*B227</f>
         <v>348.754265504643</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B224" s="19" t="n">
         <f aca="false">B223/px-1</f>
@@ -51250,7 +51672,7 @@
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B225" s="23" t="n">
         <f aca="false">B99*Y!D28</f>
@@ -51263,7 +51685,7 @@
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B226" s="23" t="n">
         <f aca="false">B98*Y!G28</f>
@@ -51276,7 +51698,7 @@
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B227" s="23" t="n">
         <f aca="false">B97*Y!J28</f>
@@ -51289,7 +51711,7 @@
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B228" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -51310,34 +51732,34 @@
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B231" s="29" t="str">
         <f aca="false">IF(B211&gt;0.5,"大於 50%",IF(B211&gt;0.25,"25%–50%",IF(B211&gt;=0,"0%–25%",IF(B211&gt;=-0.25,"0%～−25%",IF(B211&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>0%～−25%</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B232" s="29" t="str">
         <f aca="false">IF(B211&gt;0.5,"強力買進",IF(B211&gt;0.25,"買進",IF(B211&gt;=-0.25,"中立",IF(B211&gt;=-0.5,"放空","強力放空"))))</f>
         <v>中立</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>
@@ -51365,29 +51787,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>32</v>
@@ -51399,10 +51821,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -51419,10 +51841,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -51439,10 +51861,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -51459,10 +51881,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -51479,10 +51901,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -51499,10 +51921,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -51519,7 +51941,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>32</v>
@@ -51531,10 +51953,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -51551,10 +51973,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -51571,10 +51993,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -51591,10 +52013,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -51611,10 +52033,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -51631,10 +52053,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -51651,7 +52073,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>32</v>
@@ -51663,10 +52085,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -51683,10 +52105,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -51703,10 +52125,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -51723,10 +52145,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -51743,10 +52165,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -51763,10 +52185,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -51783,7 +52205,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
@@ -51795,10 +52217,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -51815,10 +52237,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -51835,10 +52257,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -51855,10 +52277,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -51875,10 +52297,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -51895,10 +52317,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -51915,32 +52337,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51948,7 +52370,7 @@
         <v>32</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -51969,10 +52391,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r+0.01))^1+Val!B186/(1+(tp_r+0.01))^2+Val!B187/(1+(tp_r+0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C185/(1+(tp_r+0.01))^1+Val!C186/(1+(tp_r+0.01))^2+Val!C187/(1+(tp_r+0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D185/(1+(tp_r+0.01))^1+Val!D186/(1+(tp_r+0.01))^2+Val!D187/(1+(tp_r+0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -51993,10 +52415,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r-0.01))^1+Val!B186/(1+(tp_r-0.01))^2+Val!B187/(1+(tp_r-0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C185/(1+(tp_r-0.01))^1+Val!C186/(1+(tp_r-0.01))^2+Val!C187/(1+(tp_r-0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D185/(1+(tp_r-0.01))^1+Val!D186/(1+(tp_r-0.01))^2+Val!D187/(1+(tp_r-0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -52017,10 +52439,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52041,10 +52463,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C44" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52065,10 +52487,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C45" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52089,10 +52511,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C46" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -52113,7 +52535,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C47" s="30" t="n">
         <f aca="false">C40-Val!B193</f>
@@ -52145,7 +52567,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52153,21 +52575,21 @@
         <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -52186,7 +52608,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -52200,12 +52622,12 @@
         <v>-0.0263064385270931</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -52219,12 +52641,12 @@
         <v>-0.0415922755838437</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!E4</f>
@@ -52238,12 +52660,12 @@
         <v>-0.0681646294175106</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!E20</f>
@@ -52257,12 +52679,12 @@
         <v>-0.111304258340884</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D4/4</f>
@@ -52276,12 +52698,12 @@
         <v>0.0884785748172741</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -52296,12 +52718,12 @@
         <v>0.102462735757573</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -52316,12 +52738,12 @@
         <v>0.175609758219222</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -52336,7 +52758,7 @@
         <v>-0.23969912582509</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/micron/dist/20261028_美光個股模型_v0.4.2.xlsx
+++ b/micron/dist/20261028_美光個股模型_v0.4.2.xlsx
@@ -378,6 +378,7 @@
     <definedName function="false" hidden="false" name="pub27" vbProcedure="false">In!$E$235</definedName>
     <definedName function="false" hidden="false" name="px" vbProcedure="false">In!$E$5</definedName>
     <definedName function="false" hidden="false" name="rf" vbProcedure="false">In!$E$31</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$250</definedName>
     <definedName function="false" hidden="false" name="sh25" vbProcedure="false">In!$E$16</definedName>
     <definedName function="false" hidden="false" name="sh25_hi" vbProcedure="false">In!$F$16</definedName>
     <definedName function="false" hidden="false" name="sh25_lo" vbProcedure="false">In!$D$16</definedName>
@@ -397,6 +398,7 @@
     <definedName function="false" hidden="false" name="tax" vbProcedure="false">In!$E$30</definedName>
     <definedName function="false" hidden="false" name="tax_hi" vbProcedure="false">In!$F$30</definedName>
     <definedName function="false" hidden="false" name="tax_lo" vbProcedure="false">In!$D$30</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$251</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$241</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$240</definedName>
     <definedName function="false" hidden="false" name="tp_roe" vbProcedure="false">In!$E$242</definedName>
@@ -480,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1106">
   <si>
     <r>
       <rPr>
@@ -3765,45 +3767,102 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">US$684</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF 933</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：本模型比共識保守：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（情境加權）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">157.33 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比共識 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">201.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.8%</t>
     </r>
     <r>
       <rPr>
@@ -3822,102 +3881,341 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 436 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">877.55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%</t>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底每股淨值比共識 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">418.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">價值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 1,714</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 708</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 322</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（現價的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.95</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.37 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍），分歧集中在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以後的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">價格路徑。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益對一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入最敏感（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±20% → ±16.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND ±30% → ±8.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±30% → ±6.5%</t>
     </r>
     <r>
       <rPr>
@@ -3936,6 +4234,198 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權重改 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使加權目標價 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+14.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。下一個檢驗事件是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FQ1 FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下旬）的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合約價與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出貨。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Comparable </t>
     </r>
     <r>
@@ -3945,189 +4435,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">單獨為 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。兩法差距來自倍數：記憶體同業前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.51 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底每股淨值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">289.40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，遠低於共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,560.57 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隱含的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.73 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍（比同業高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">148%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；美光自身前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/B 3.35 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍，因大量買回壓低帳面淨值。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
     </r>
     <r>
       <rPr>
@@ -4146,101 +4625,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：本模型比共識保守：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（情境加權）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">157.33 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">201.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">、</t>
     </r>
     <r>
@@ -4251,521 +4635,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底每股淨值比共識 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">418.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">價值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 1,714</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 708</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 322</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（現價的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.95</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.37 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍），分歧集中在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以後的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">價格路徑。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益對一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入最敏感（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±20% → ±16.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND ±30% → ±8.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM ±30% → ±6.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">權重改 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使加權目標價 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+14.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。下一個檢驗事件是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FQ1 FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下旬）的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">合約價與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出貨。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -35314,116 +35212,13 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× (1 − </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業費用變動率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">輸入變動</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Δ</t>
+      <t xml:space="preserve">0.5 </t>
     </r>
     <r>
       <rPr>
@@ -35432,324 +35227,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">營業利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（價格或份額）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Y </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">欄。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標價參數（只改 </t>
+      <t xml:space="preserve">相對倍數調整（</t>
     </r>
     <r>
       <rPr>
@@ -35759,7 +35237,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -35768,7 +35246,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">參數；</t>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
     </r>
     <r>
       <rPr>
@@ -35778,7 +35256,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Y </t>
+      <t xml:space="preserve">× </t>
     </r>
     <r>
       <rPr>
@@ -35787,7 +35265,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頁收斂法的 </t>
+      <t xml:space="preserve">本公司 </t>
     </r>
     <r>
       <rPr>
@@ -35797,7 +35275,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">fade_g </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -35806,7 +35284,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不隨 </t>
+      <t xml:space="preserve">年相對同業的 </t>
     </r>
     <r>
       <rPr>
@@ -35816,7 +35294,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tp_g </t>
+      <t xml:space="preserve">P/B </t>
     </r>
     <r>
       <rPr>
@@ -35825,16 +35303,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">變動）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
+      <t xml:space="preserve">比；</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -35843,7 +35313,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
     </r>
     <r>
       <rPr>
@@ -35852,8 +35322,343 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價</t>
-    </r>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
   </si>
   <si>
     <r>
@@ -35864,7 +35669,1196 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美光</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg MU US Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 000660 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 005930 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 285A JT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2408 TT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (1 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業費用變動率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">輸入變動</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">營業利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（價格或份額）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價參數（只改 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參數；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁收斂法的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">fade_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不隨 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tp_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變動）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
     </r>
     <r>
       <rPr>
@@ -37678,7 +38672,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -37796,6 +38790,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -38055,7 +39053,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -38197,17 +39195,23 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
+      <c r="A29" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 US$"&amp;TEXT(Val!$B$208,"#,##0.00")&amp;"（DCF "&amp;TEXT(Val!$B$193,"#,##0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$211&gt;=0,"高 "&amp;TEXT(Val!$B$211,"0.0%"),"低 "&amp;TEXT(-Val!$B$211,"0.0%"))&amp;"，級距 "&amp;Val!$B$231&amp;"、投資建議 "&amp;Val!$B$232&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$193+(1-tp_w_dcf)*Val!$B$203)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$212,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：兩法差距來自倍數：記憶體同業前瞻 P/B 中位數 1.51 倍 × FY2028 年底每股淨值 289.40，遠低於共識目標價 1,560.57 隱含的 3.73 倍（比同業高 148%）；美光自身前瞻 P/B 3.35 倍，因大量買回壓低帳面淨值。"</f>
+        <v>重點觀察 1：目標價 US$750.20（DCF 932.63、Comparable（相對倍數調整後）567.77；DCF 權重 50%），比現價 877.55（2026-10-23）低 14.5%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 1.30（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −22.0%；Comparable 單獨（市場主流同業法、未調整）為 −50.4%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：兩法差距來自倍數：記憶體同業前瞻 P/B 中位數 1.51 倍 × FY2028 年底每股淨值 289.40，遠低於共識目標價 1,560.57 隱含的 3.73 倍（比同業高 148%）；美光自身前瞻 P/B 3.35 倍，因大量買回壓低帳面淨值。</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>26</v>
       </c>
     </row>
@@ -38236,12 +39240,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1037</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1038</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
@@ -38253,7 +39257,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -38265,7 +39269,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1040</v>
+        <v>1079</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
@@ -38277,7 +39281,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1041</v>
+        <v>1080</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
@@ -38289,10 +39293,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1043</v>
+        <v>1082</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>44</v>
@@ -38328,98 +39332,98 @@
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1044</v>
+        <v>1083</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1045</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1046</v>
+        <v>1085</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1047</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1049</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1050</v>
+        <v>1089</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1051</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1052</v>
+        <v>1091</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1053</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1054</v>
+        <v>1093</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1055</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1057</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1058</v>
+        <v>1097</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1059</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1060</v>
+        <v>1099</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1062</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1063</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1064</v>
+        <v>1103</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1066</v>
+        <v>1105</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -48172,7 +49176,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:Q251"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -51484,8 +52488,8 @@
         <v>953</v>
       </c>
       <c r="B208" s="27" t="n">
-        <f aca="false">tp_w_dcf*B193+(1-tp_w_dcf)*B203</f>
-        <v>684.089469121124</v>
+        <f aca="false">tp_w_dcf*B193+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>750.197823374767</v>
       </c>
       <c r="E208" s="8" t="s">
         <v>954</v>
@@ -51518,7 +52522,7 @@
       </c>
       <c r="B211" s="19" t="n">
         <f aca="false">B208/px-1</f>
-        <v>-0.220455279902998</v>
+        <v>-0.145122416529238</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>958</v>
@@ -51760,6 +52764,413 @@
       </c>
       <c r="E232" s="4" t="s">
         <v>985</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="6" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="4" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="D237" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="E237" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="F237" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="G237" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="H237" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="I237" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="J237" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="K237" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="L237" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="M237" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="N237" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O237" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="P237" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="Q237" s="5" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B238" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D238" s="18" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E238" s="18" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="F238" s="18" t="n">
+        <v>1.2295</v>
+      </c>
+      <c r="G238" s="18" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="H238" s="18" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="I238" s="18" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="J238" s="18" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="K238" s="18" t="n">
+        <v>2.1515</v>
+      </c>
+      <c r="L238" s="18" t="n">
+        <v>1.898</v>
+      </c>
+      <c r="M238" s="18" t="n">
+        <v>3.5655</v>
+      </c>
+      <c r="N238" s="8" t="n">
+        <f aca="false">COUNT(D238:M238)</f>
+        <v>10</v>
+      </c>
+      <c r="O238" s="14" t="n">
+        <f aca="false">IF(N238&gt;0,MEDIAN(D238:M238),"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="P238" s="14" t="n">
+        <f aca="false">IF(N238&gt;=7,O238,"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="Q238" s="8" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="B239" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D239" s="18" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="E239" s="18" t="n">
+        <v>1.1395</v>
+      </c>
+      <c r="F239" s="18" t="n">
+        <v>0.9995</v>
+      </c>
+      <c r="G239" s="18" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="H239" s="18" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="I239" s="18" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="J239" s="18" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="K239" s="18" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="L239" s="18" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="M239" s="18" t="n">
+        <v>2.3405</v>
+      </c>
+      <c r="N239" s="8" t="n">
+        <f aca="false">COUNT(D239:M239)</f>
+        <v>10</v>
+      </c>
+      <c r="O239" s="14" t="n">
+        <f aca="false">IF(N239&gt;0,MEDIAN(D239:M239),"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="P239" s="14" t="n">
+        <f aca="false">IF(N239&gt;=7,O239,"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="Q239" s="8" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="B240" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D240" s="18" t="n">
+        <v>1.4135</v>
+      </c>
+      <c r="E240" s="18" t="n">
+        <v>1.2645</v>
+      </c>
+      <c r="F240" s="18" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="G240" s="18" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="H240" s="18" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="I240" s="18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J240" s="18" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K240" s="18" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L240" s="18" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="M240" s="18" t="n">
+        <v>1.8275</v>
+      </c>
+      <c r="N240" s="8" t="n">
+        <f aca="false">COUNT(D240:M240)</f>
+        <v>10</v>
+      </c>
+      <c r="O240" s="14" t="n">
+        <f aca="false">IF(N240&gt;0,MEDIAN(D240:M240),"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="P240" s="14" t="n">
+        <f aca="false">IF(N240&gt;=7,O240,"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="Q240" s="8" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="B241" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L241" s="18" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="M241" s="18" t="n">
+        <v>3.9425</v>
+      </c>
+      <c r="N241" s="8" t="n">
+        <f aca="false">COUNT(D241:M241)</f>
+        <v>2</v>
+      </c>
+      <c r="O241" s="14" t="n">
+        <f aca="false">IF(N241&gt;0,MEDIAN(D241:M241),"")</f>
+        <v>2.71825</v>
+      </c>
+      <c r="P241" s="14" t="str">
+        <f aca="false">IF(N241&gt;=7,O241,"")</f>
+        <v/>
+      </c>
+      <c r="Q241" s="8" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="B242" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D242" s="18" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="E242" s="18" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="F242" s="18" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="G242" s="18" t="n">
+        <v>1.1455</v>
+      </c>
+      <c r="H242" s="18" t="n">
+        <v>1.3955</v>
+      </c>
+      <c r="I242" s="18" t="n">
+        <v>1.0635</v>
+      </c>
+      <c r="J242" s="18" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="K242" s="18" t="n">
+        <v>1.1785</v>
+      </c>
+      <c r="L242" s="18" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="M242" s="18" t="n">
+        <v>2.7665</v>
+      </c>
+      <c r="N242" s="8" t="n">
+        <f aca="false">COUNT(D242:M242)</f>
+        <v>10</v>
+      </c>
+      <c r="O242" s="14" t="n">
+        <f aca="false">IF(N242&gt;0,MEDIAN(D242:M242),"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="P242" s="14" t="n">
+        <f aca="false">IF(N242&gt;=7,O242,"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="Q242" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B244" s="14" t="n">
+        <f aca="false">P238</f>
+        <v>1.62</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B245" s="16" t="n">
+        <f aca="false">COUNT(P239:P242)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B246" s="14" t="n">
+        <f aca="false">IF(B245&gt;0,MEDIAN(P239:P242),"")</f>
+        <v>1.24275</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B247" s="14" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B244),B245&gt;=2),B244/B246,"")</f>
+        <v>1.30356065178033</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B248" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B249" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B250" s="30" t="n">
+        <f aca="false">IF(ISNUMBER(B247),MIN(MAX(B247,B248),B249),1)</f>
+        <v>1.30356065178033</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B251" s="27" t="n">
+        <f aca="false">Val!$B$203*B250</f>
+        <v>567.769563371247</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>1025</v>
       </c>
     </row>
   </sheetData>
@@ -51787,24 +53198,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>990</v>
+        <v>1030</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>991</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51824,7 +53235,7 @@
         <v>758</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -51844,7 +53255,7 @@
         <v>758</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -51864,7 +53275,7 @@
         <v>758</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -51884,7 +53295,7 @@
         <v>758</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -51904,7 +53315,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -51924,7 +53335,7 @@
         <v>758</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -51956,7 +53367,7 @@
         <v>762</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -51976,7 +53387,7 @@
         <v>762</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -51996,7 +53407,7 @@
         <v>762</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -52016,7 +53427,7 @@
         <v>762</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -52036,7 +53447,7 @@
         <v>762</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -52056,7 +53467,7 @@
         <v>762</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -52088,7 +53499,7 @@
         <v>765</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -52108,7 +53519,7 @@
         <v>765</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -52128,7 +53539,7 @@
         <v>765</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -52148,7 +53559,7 @@
         <v>765</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -52168,7 +53579,7 @@
         <v>765</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -52188,7 +53599,7 @@
         <v>765</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -52220,7 +53631,7 @@
         <v>766</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -52240,7 +53651,7 @@
         <v>766</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -52260,7 +53671,7 @@
         <v>766</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -52280,7 +53691,7 @@
         <v>766</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -52300,7 +53711,7 @@
         <v>766</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -52320,7 +53731,7 @@
         <v>766</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -52337,32 +53748,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1004</v>
+        <v>1043</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>991</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52370,19 +53781,19 @@
         <v>32</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1005</v>
+        <v>1044</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>932.626083378287</v>
       </c>
       <c r="D40" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E40" s="23" t="n">
         <f aca="false">tp_w_dcf*C40+(1-tp_w_dcf)*D40</f>
-        <v>684.089469121124</v>
+        <v>750.197823374767</v>
       </c>
       <c r="F40" s="19" t="n">
         <f aca="false">E40/E$40-1</f>
@@ -52391,153 +53802,153 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1006</v>
+        <v>1045</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1007</v>
+        <v>1046</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r+0.01))^1+Val!B186/(1+(tp_r+0.01))^2+Val!B187/(1+(tp_r+0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C185/(1+(tp_r+0.01))^1+Val!C186/(1+(tp_r+0.01))^2+Val!C187/(1+(tp_r+0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D185/(1+(tp_r+0.01))^1+Val!D186/(1+(tp_r+0.01))^2+Val!D187/(1+(tp_r+0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
         <v>848.800712492664</v>
       </c>
       <c r="D41" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E41" s="23" t="n">
         <f aca="false">tp_w_dcf*C41+(1-tp_w_dcf)*D41</f>
-        <v>642.176783678313</v>
+        <v>708.285137931955</v>
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">E41/E$40-1</f>
-        <v>-0.0612678419047416</v>
+        <v>-0.0558688443726313</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>1008</v>
+        <v>1047</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1009</v>
+        <v>1048</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r-0.01))^1+Val!B186/(1+(tp_r-0.01))^2+Val!B187/(1+(tp_r-0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C185/(1+(tp_r-0.01))^1+Val!C186/(1+(tp_r-0.01))^2+Val!C187/(1+(tp_r-0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D185/(1+(tp_r-0.01))^1+Val!D186/(1+(tp_r-0.01))^2+Val!D187/(1+(tp_r-0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
         <v>1048.41834409856</v>
       </c>
       <c r="D42" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">tp_w_dcf*C42+(1-tp_w_dcf)*D42</f>
-        <v>741.985599481259</v>
+        <v>808.093953734902</v>
       </c>
       <c r="F42" s="19" t="n">
         <f aca="false">E42/E$40-1</f>
-        <v>0.0846323952837873</v>
+        <v>0.0771744845908633</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1010</v>
+        <v>1049</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1011</v>
+        <v>1050</v>
       </c>
       <c r="C43" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>1000.68764201379</v>
       </c>
       <c r="D43" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">tp_w_dcf*C43+(1-tp_w_dcf)*D43</f>
-        <v>718.120248438876</v>
+        <v>784.228602692519</v>
       </c>
       <c r="F43" s="19" t="n">
         <f aca="false">E43/E$40-1</f>
-        <v>0.0497460944128736</v>
+        <v>0.0453624074309689</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1012</v>
+        <v>1051</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1013</v>
+        <v>1052</v>
       </c>
       <c r="C44" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>885.185900644397</v>
       </c>
       <c r="D44" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E44" s="23" t="n">
         <f aca="false">tp_w_dcf*C44+(1-tp_w_dcf)*D44</f>
-        <v>660.369377754179</v>
+        <v>726.477732007822</v>
       </c>
       <c r="F44" s="19" t="n">
         <f aca="false">E44/E$40-1</f>
-        <v>-0.0346739606990572</v>
+        <v>-0.0316184486649667</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1015</v>
+        <v>1054</v>
       </c>
       <c r="C45" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>932.626083378287</v>
       </c>
       <c r="D45" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E45" s="23" t="n">
         <f aca="false">0.3*C45+(1-0.3)*D45</f>
-        <v>584.674823418259</v>
+        <v>677.226519373359</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">E45/E$40-1</f>
-        <v>-0.145324040480534</v>
+        <v>-0.097269415783088</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1016</v>
+        <v>1055</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1017</v>
+        <v>1056</v>
       </c>
       <c r="C46" s="23" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>932.626083378287</v>
       </c>
       <c r="D46" s="23" t="n">
-        <f aca="false">Val!B203</f>
-        <v>435.552854863962</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>567.769563371247</v>
       </c>
       <c r="E46" s="23" t="n">
         <f aca="false">0.7*C46+(1-0.7)*D46</f>
-        <v>783.504114823989</v>
+        <v>823.169127376175</v>
       </c>
       <c r="F46" s="19" t="n">
         <f aca="false">E46/E$40-1</f>
-        <v>0.145324040480534</v>
+        <v>0.0972694157830882</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C47" s="30" t="n">
+        <v>1057</v>
+      </c>
+      <c r="C47" s="31" t="n">
         <f aca="false">C40-Val!B193</f>
         <v>0</v>
       </c>
@@ -52567,7 +53978,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1019</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52575,21 +53986,21 @@
         <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1020</v>
+        <v>1059</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1023</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1024</v>
+        <v>1063</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -52608,7 +54019,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1025</v>
+        <v>1064</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -52622,12 +54033,12 @@
         <v>-0.0263064385270931</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1026</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1027</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -52641,12 +54052,12 @@
         <v>-0.0415922755838437</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1028</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1029</v>
+        <v>1068</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!E4</f>
@@ -52660,12 +54071,12 @@
         <v>-0.0681646294175106</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1030</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1031</v>
+        <v>1070</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!E20</f>
@@ -52679,12 +54090,12 @@
         <v>-0.111304258340884</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1028</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D4/4</f>
@@ -52698,12 +54109,12 @@
         <v>0.0884785748172741</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1033</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1034</v>
+        <v>1073</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -52723,7 +54134,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1035</v>
+        <v>1074</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -52743,7 +54154,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1036</v>
+        <v>1075</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E28</f>
